--- a/download/sample_report_grocery.xlsx
+++ b/download/sample_report_grocery.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Analysis" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory Alerts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory Management" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Analysis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,9 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -112,21 +114,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -141,6 +143,9 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -150,14 +155,7 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -166,20 +164,33 @@
     <xf numFmtId="3" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -188,7 +199,6 @@
   <dxfs count="4">
     <dxf>
       <font>
-        <b val="1"/>
         <color rgb="00C0392B"/>
       </font>
       <fill>
@@ -199,7 +209,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color rgb="00D4820A"/>
       </font>
       <fill>
@@ -210,7 +219,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color rgb="001B7D46"/>
       </font>
       <fill>
@@ -221,7 +229,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color rgb="001B2A4A"/>
       </font>
       <fill>
@@ -323,7 +330,7 @@
                 <a:latin typeface="Noto Sans CJK SC"/>
                 <a:ea typeface="Noto Sans CJK SC"/>
               </a:rPr>
-              <a:t>Revenue vs Expenses by Month</a:t>
+              <a:t>Revenue vs Expenses</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -337,9 +344,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Dashboard'!C8</f>
-            </strRef>
+            <v>Revenue</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -354,12 +359,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$9:$B$12</f>
+              <f>'Executive Summary'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$C$9:$C$12</f>
+              <f>'Executive Summary'!$C$7:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -367,34 +372,32 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <strRef>
-              <f>'Dashboard'!D8</f>
-            </strRef>
+            <v>Expenses</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="D4820A"/>
+              <a:srgbClr val="1B7D46"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="D4820A"/>
+                <a:srgbClr val="1B7D46"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$9:$B$12</f>
+              <f>'Executive Summary'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$9:$D$12</f>
+              <f>'Executive Summary'!$D$7:$D$13</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="100"/>
-        <overlap val="0"/>
+        <gapWidth val="80"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -432,8 +435,7 @@
                     <a:latin typeface="Noto Sans CJK SC"/>
                     <a:ea typeface="Noto Sans CJK SC"/>
                   </a:rPr>
-                  <a:t>Amount 
-(AED)</a:t>
+                  <a:t>AED</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -459,7 +461,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -500,17 +502,15 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Dashboard'!F8</f>
-            </strRef>
+            <v>Profit Margin</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1B7D46"/>
+              <a:srgbClr val="1B2A4A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="1B7D46"/>
+                <a:srgbClr val="1B2A4A"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -525,15 +525,14 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$9:$B$12</f>
+              <f>'Executive Summary'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$F$9:$F$12</f>
+              <f>'Executive Summary'!$E$7:$E$13</f>
             </numRef>
           </val>
-          <smooth val="1"/>
         </ser>
         <axId val="10"/>
         <axId val="100"/>
@@ -553,8 +552,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.25"/>
-          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -594,12 +591,14 @@
             </a:p>
           </txPr>
         </title>
-        <numFmt formatCode="0.0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -626,7 +625,143 @@
                 <a:latin typeface="Noto Sans CJK SC"/>
                 <a:ea typeface="Noto Sans CJK SC"/>
               </a:rPr>
-              <a:t>Revenue by Product (AED)</a:t>
+              <a:t>Monthly Transactions</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Transactions</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1B2A4A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1B2A4A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Executive Summary'!$B$8:$B$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Executive Summary'!$G$7:$G$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:rPr>
+                  <a:t>Count</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Top Products by Revenue</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -640,9 +775,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Product Analysis'!E5</f>
-            </strRef>
+            <v>Revenue (AED)</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -657,12 +790,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Product Analysis'!$B$6:$B$15</f>
+              <f>'Product Analysis'!$B$5:$B$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Product Analysis'!$E$6:$E$15</f>
+              <f>'Product Analysis'!$E$4:$E$19</f>
             </numRef>
           </val>
         </ser>
@@ -677,10 +810,22 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
               <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0">
@@ -693,36 +838,41 @@
                     <a:latin typeface="Noto Sans CJK SC"/>
                     <a:ea typeface="Noto Sans CJK SC"/>
                   </a:rPr>
-                  <a:t>Revenue (AED)</a:t>
+                  <a:t>AED</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
         </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -754,11 +904,6 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Product Analysis'!K5</f>
-            </strRef>
-          </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -874,24 +1019,407 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="10"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="1B2A4A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'Product Analysis'!$J$6:$J$15</f>
+              <f>'Product Analysis'!$B$24:$B$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Product Analysis'!$K$6:$K$15</f>
+              <f>'Product Analysis'!$C$23:$C$34</f>
             </numRef>
           </val>
         </ser>
-        <dLbls>
-          <showVal val="0"/>
-          <showCatName val="1"/>
-          <showPercent val="1"/>
-        </dLbls>
         <firstSliceAng val="0"/>
       </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Margin by Category</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Avg Margin</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1B2A4A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1B2A4A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Product Analysis'!$B$24:$B$34</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Product Analysis'!$E$23:$E$34</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="80"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:rPr>
+                  <a:t>Margin</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Revenue by Customer Segment</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="1B2A4A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="1B7D46"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="D4820A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8C8A84"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'Customer Analysis'!$B$5:$B$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Customer Analysis'!$F$4:$F$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Revenue by Day of Week</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Revenue (AED)</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1B2A4A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1B2A4A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Customer Analysis'!$B$30:$B$36</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Customer Analysis'!$C$29:$C$36</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="80"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:rPr>
+                  <a:t>AED</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
@@ -911,7 +1439,149 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="3600000"/>
+    <ext cx="6480000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -930,59 +1600,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="3960000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5760000" cy="3960000"/>
+    <ext cx="5040000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1289,175 +1910,298 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H47"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Al Madina Grocery — Monthly Business Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>January 2026 | Ajman, UAE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="B5" s="3" t="n">
-        <v>312800</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>268400</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>44400</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0.142</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="5" t="inlineStr">
+          <t>Al Madina Grocery — Executive Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Net Profit</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Profit Margin</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Total Transactions</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Avg Basket Size</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="C5" s="3" t="n">
+        <v>2634500</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1928600</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>705900</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.2679</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>48750</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>54.04</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7" ht="28" customHeight="1">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Revenue (AED)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Expenses (AED)</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Net Profit (AED)</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Profit Margin</t>
         </is>
       </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Transactions</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Avg Basket (AED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>398200</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>296500</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>101700</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>7200</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>55.31</v>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>412800</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>305200</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>107600</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>7450</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>55.41</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
-        <v>285600</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>252100</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>33500</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>0.117</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="C10" s="8" t="n">
+        <v>435600</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>318400</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>117200</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0.2691</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>7820</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>298400</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>259800</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>38600</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>0.129</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="C11" s="12" t="n">
+        <v>448900</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>327800</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>121100</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>8100</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>55.42</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
-        <v>342100</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>278500</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>63600</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>0.186</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="C12" s="8" t="n">
+        <v>467200</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>338500</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>128700</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>8500</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>54.96</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>312800</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>268400</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>44400</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>0.142</v>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14"/>
+      <c r="C13" s="12" t="n">
+        <v>472000</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>342200</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>129800</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>9680</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>48.76</v>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>2634500</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>1928600</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>705900</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>0.2679</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>48750</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>54.04</v>
+      </c>
+    </row>
     <row r="15"/>
     <row r="16"/>
     <row r="17"/>
@@ -1475,33 +2219,17 @@
     <row r="29"/>
     <row r="30"/>
     <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47" ht="20" customHeight="1">
-      <c r="B47" s="2" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="B2:H2"/>
+  <mergeCells count="2">
+    <mergeCell ref="B32:M32"/>
+    <mergeCell ref="B2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1514,437 +2242,759 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:K52"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Top Products — January 2026</t>
+          <t>Product Performance — January 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="8" customHeight="1"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="B5" s="6" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Units Sold</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Revenue (AED)</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Unit Price (AED)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Cost Price (AED)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Profit Margin</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>Revenue (AED)</t>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Stock Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Al Ain Water (24pk)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>2850</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Adequate</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Basmati Rice (25kg)</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Grains</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>420</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>33600</v>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Basmati Rice (5kg)</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Grains &amp; Pulses</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>1920</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>76800</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Grains</t>
-        </is>
-      </c>
-      <c r="K6" s="15" t="n">
-        <v>33600</v>
+        <v>40</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Fresh Chicken (kg)</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Meat</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>680</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>27200</v>
-      </c>
-      <c r="F7" s="16" t="n">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Fresh Chicken (1kg)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Meat &amp; Poultry</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>2340</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>70200</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Low Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Olive Oil (1L)</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Cooking Essentials</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>1680</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>67200</v>
+      </c>
+      <c r="F8" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="G7" s="12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Meat</t>
-        </is>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>27200</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Cooking Oil (5L)</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Oil &amp; Ghee</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>540</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>24300</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Oil &amp; Ghee</t>
-        </is>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>24300</v>
+      <c r="G8" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Fresh Milk (1L)</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Labneh (500g)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Dairy</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>8400</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="D9" s="8" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Arabic Bread (10pk)</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>Surplus</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Dates (1kg)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Dry Fruits</t>
         </is>
       </c>
-      <c r="K9" s="15" t="n">
-        <v>12400</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Bread (pack)</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Bakery</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>950</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>4750</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="D11" s="8" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>43500</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Milk (2L)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Dairy</t>
         </is>
       </c>
-      <c r="K10" s="15" t="n">
-        <v>8400</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Dates (1kg)</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Dry Fruits</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>310</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>12400</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Household</t>
-        </is>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>8400</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Spices Mix</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Spices</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>480</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>7200</v>
+      <c r="D12" s="12" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>42000</v>
       </c>
       <c r="F12" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="G12" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Low Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Coca-Cola (12pk)</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>1950</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>39000</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Saffron (1g)</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Spices</t>
         </is>
       </c>
-      <c r="K12" s="15" t="n">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Water (24-pack)</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="D14" s="12" t="n">
+        <v>680</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Frozen Falafel (1kg)</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Frozen Foods</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>23400</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Honey (500g)</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Dry Fruits</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>920</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>36800</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>Low Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Laundry Detergent</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Household</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>27600</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Diapers (Large)</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Baby Care</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>33000</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Tea Bags (100pk)</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Beverages</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
-        <v>890</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>5340</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>5340</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Canned Beans</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Canned Food</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>620</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>4960</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Canned Food</t>
-        </is>
-      </c>
-      <c r="K14" s="15" t="n">
-        <v>4960</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Laundry Detergent</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Household</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>280</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>8400</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Bakery</t>
-        </is>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>4750</v>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>6370</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>136550</v>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
+      <c r="D19" s="8" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>41000</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Surplus</t>
+        </is>
+      </c>
+    </row>
     <row r="20"/>
     <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
+    <row r="22">
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Category Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Revenue (AED)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>% of Revenue</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Avg Margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>137000</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.2195</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Grains &amp; Pulses</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>76800</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Meat &amp; Poultry</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>70200</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.267</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Cooking Essentials</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>67200</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>79800</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0.361</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>32000</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Dry Fruits</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>80300</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Spices</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>34000</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Frozen Foods</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>23400</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Household</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>27600</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Baby Care</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>33000</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
     <row r="35"/>
     <row r="36"/>
     <row r="37"/>
@@ -1963,7 +3013,7 @@
     <row r="50"/>
     <row r="51"/>
     <row r="52" ht="20" customHeight="1">
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
         </is>
@@ -1971,8 +3021,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B52:J52"/>
+    <mergeCell ref="B2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1985,363 +3035,969 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H17"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Inventory Status &amp; Reorder Alerts</t>
+          <t>Inventory &amp; Supply Chain — January 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="8" customHeight="1"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="B5" s="6" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Current Stock</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Reorder Level</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Days of Supply</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Action Required</t>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Last Order Date</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Lead Time (days)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Al Ain Water (24pk)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>450</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Al Ain Foods</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Basmati Rice (25kg)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>85 bags</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>100 bags</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Basmati Rice (5kg)</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Al Khaleej Rice</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Fresh Chicken (1kg)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Low Stock</t>
         </is>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F7" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Al Rawdah</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Reorder Now</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Olive Oil (1L)</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Filipppo Berio</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Labneh (500g)</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Almarai</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Arabic Bread (10pk)</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>520</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Surplus</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Modern Bakery</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>Reduce Order</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Dates (1kg)</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Low Stock</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Al Foah</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Reorder Now</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Fresh Chicken (kg)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>45 kg</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>50 kg</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Milk (2L)</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Low Stock</t>
         </is>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F12" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Almarai</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>Reorder Now</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Coca-Cola (12pk)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>160</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Coca-Cola MEA</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Saffron (1g)</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Reorder Urgent</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Cooking Oil (5L)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>180 bottles</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>100 bottles</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Iranian Spice Co</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Urgent Reorder</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Frozen Falafel (1kg)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>130</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Adequate</t>
         </is>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Al Areesh</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Honey (500g)</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Low Stock</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Al Shifa</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>Reorder Now</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Laundry Detergent</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Unilever MEA</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Diapers (Large)</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Adequate</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>P&amp;G MEA</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Tea Bags (100pk)</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>280</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Surplus</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>No Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Fresh Milk (1L)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>320 units</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>200 units</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>Adequate</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="n">
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Lipton MEA</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Reduce Order</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Supplier Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Products</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Total Orders</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>On-Time Delivery %</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Almarai</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Al Ain Foods</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F25" s="24" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Al Khaleej Rice</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F26" s="23" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Al Rawdah</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F27" s="24" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Filipppo Berio</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F28" s="23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Al Foah</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>No Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Bread (pack)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>60 packs</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>100 packs</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>Low Stock</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Reorder Urgent</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Dates (1kg)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>150 boxes</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>80 boxes</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>Surplus</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>35</v>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>Reduce Order</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Spices Mix</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>200 packs</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>100 packs</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>Adequate</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>28</v>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>No Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Water (24-pack)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>40 packs</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>150 packs</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Reorder Urgent</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Canned Beans</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>300 cans</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>150 cans</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>Adequate</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="n">
+      <c r="E29" s="13" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F29" s="24" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Coca-Cola MEA</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F30" s="23" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Iranian Spice Co</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F31" s="24" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Al Areesh</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F32" s="23" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Al Shifa</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F33" s="24" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Unilever MEA</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F34" s="23" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>P&amp;G MEA</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F35" s="24" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Lipton MEA</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F36" s="23" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Modern Bakery</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>No Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Laundry Detergent</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>25 units</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>50 units</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>Low Stock</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Reorder Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="2" t="inlineStr">
+      <c r="E37" s="13" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F37" s="24" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40" ht="20" customHeight="1">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
         </is>
@@ -2349,10 +4005,10 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="B2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E15">
+  <conditionalFormatting sqref="E5:E19">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Critical"</formula>
     </cfRule>
@@ -2366,6 +4022,17 @@
       <formula>"Surplus"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J19">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
+      <formula>"Urgent Reorder"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="1">
+      <formula>"Reorder Now"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="3">
+      <formula>"Reduce Order"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2376,120 +4043,339 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E12"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Key Insights &amp; Recommendations</t>
+          <t>Customer Insights — January 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="8" customHeight="1"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
+    <row r="4" ht="28" customHeight="1">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Avg Spend (AED)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Visits/Month</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue (AED)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>% of Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Daily Shoppers</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>2188800</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0.4635</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Weekly Families</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>612000</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>0.1297</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Monthly Bulk</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>650</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Water inventory is at critical level (2 days supply). Immediate reorder needed.</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="23" t="n">
+      <c r="F7" s="8" t="n">
+        <v>136500</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>0.0289</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Occasional</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="E8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Fresh bread and chicken are below reorder levels. Daily deliveries need adjustment.</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="21" t="n">
+      <c r="F8" s="12" t="n">
+        <v>184800</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0.0392</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>750</v>
+      </c>
+      <c r="E9" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Dates have 35 days of supply — surplus. Reduce next order by 40%.</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Spices have highest margin (55%) but only 4.4% of revenue. Consider promotional display.</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>December revenue spike (AED 342,100) was seasonal. Stock planning needed for Q4 2026.</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
+      <c r="F9" s="8" t="n">
+        <v>191250</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>0.0405</v>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11"/>
-    <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29" ht="28" customHeight="1">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Revenue (AED)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Transactions</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Avg Basket (AED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>82000</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>1680</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>48.81</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>68000</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>1420</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>47.89</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>58000</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>1180</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>49.15</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>55000</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>49.11</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>1240</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>48.39</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>1350</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>48.15</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>84500</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>1780</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>47.47</v>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50" ht="20" customHeight="1">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
         </is>
@@ -2497,10 +4383,329 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B50:I50"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D10">
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1"/>
+    <row r="2" ht="32" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Key Insights &amp; Strategic Recommendations</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Action Item</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Saffron stock is critical (3 days of supply) with 10-day lead time</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Place urgent reorder with Iranian Spice Co; identify backup supplier</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Daily Shoppers contribute 46% of revenue but have low avg spend (AED 28.50)</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Implement cross-sell promotions at checkout to increase basket size</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Supply Chain</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Arabic Bread surplus (28 days) with high waste risk</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Reduce order quantity by 40% and negotiate smaller daily deliveries</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale segment has highest avg spend (AED 750) but only 85 customers</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Launch B2B loyalty program with volume discounts to grow this segment</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Weekend revenue (Fri+Sat) is 35% of weekly total</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Extend weekend hours and add promotional displays at entrance</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Fresh Chicken margin (26.7%) is lowest across all products</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Renegotiate supplier terms or increase retail price by AED 2/kg</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Milk and Dates are below reorder level with high turnover</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Set up automated reorder triggers when stock hits 120% of reorder level</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Monthly bulk buyers visit only once — potential for repeat purchase</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Introduce subscription boxes with home delivery for bulk items</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B15:H15"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G5:G12">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"High"</formula>
     </cfRule>
@@ -2511,6 +4716,14 @@
       <formula>"Low"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E12">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"High"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>"Medium"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>